--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486951_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486951_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. SANCHEZ PERDIGUERO</t>
+          <t>A. LIBROIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5094</v>
+        <v>5.4591</v>
       </c>
       <c r="E2" t="n">
-        <v>4.6153</v>
+        <v>4.3274</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8941</v>
+        <v>1.1317</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3428</v>
+        <v>3.7836</v>
       </c>
       <c r="H2" t="n">
-        <v>4.2271</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>1.1158</v>
+        <v>3.2124</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2839</v>
+        <v>5.0475</v>
       </c>
       <c r="K2" t="n">
-        <v>4.192</v>
+        <v>2.2328</v>
       </c>
       <c r="L2" t="n">
-        <v>0.092</v>
+        <v>2.8147</v>
       </c>
       <c r="M2" t="n">
-        <v>1.0589</v>
+        <v>-1.2639</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0351</v>
+        <v>-1.6616</v>
       </c>
       <c r="O2" t="n">
-        <v>1.0238</v>
+        <v>0.3977</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8214</v>
+        <v>0.616</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0534</v>
+        <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8586</v>
+        <v>-0.1191</v>
       </c>
       <c r="T2" t="n">
-        <v>2.7195</v>
+        <v>0.1547</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1391</v>
+        <v>-0.2739</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.5134</v>
+        <v>1.1786</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.1561</v>
+        <v>1.1786</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.3573</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A. LIBROIA</t>
+          <t>A. SANCHEZ PERDIGUERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.8894</v>
+        <v>3.8781</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0838</v>
+        <v>2.9029</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8056</v>
+        <v>0.9752</v>
       </c>
       <c r="G3" t="n">
-        <v>3.7836</v>
+        <v>5.3428</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5711000000000001</v>
+        <v>4.2271</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2124</v>
+        <v>1.1158</v>
       </c>
       <c r="J3" t="n">
-        <v>5.0475</v>
+        <v>4.2839</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2328</v>
+        <v>4.192</v>
       </c>
       <c r="L3" t="n">
-        <v>2.8147</v>
+        <v>0.092</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2639</v>
+        <v>1.0589</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.6616</v>
+        <v>0.0351</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3977</v>
+        <v>1.0238</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>0.8214</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R3" t="n">
-        <v>2.6694</v>
+        <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6888</v>
+        <v>1.2273</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0889</v>
+        <v>1.0071</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5999</v>
+        <v>0.2202</v>
       </c>
       <c r="V3" t="n">
-        <v>1.1786</v>
+        <v>-3.5134</v>
       </c>
       <c r="W3" t="n">
-        <v>1.1786</v>
+        <v>-1.1561</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4469</v>
+        <v>3.1683</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1466</v>
+        <v>2.6309</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3003</v>
+        <v>0.5375</v>
       </c>
       <c r="G4" t="n">
         <v>0.8043</v>
@@ -766,13 +766,13 @@
         <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1231</v>
+        <v>0.8445</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2013</v>
+        <v>0.6856</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="V4" t="n">
         <v>0.6982</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3459</v>
+        <v>0.546</v>
       </c>
       <c r="E5" t="n">
-        <v>0.96</v>
+        <v>1.1304</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6141</v>
+        <v>-0.5844</v>
       </c>
       <c r="G5" t="n">
         <v>0.5237000000000001</v>
@@ -844,13 +844,13 @@
         <v>0.2053</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3832</v>
+        <v>-0.1831</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2635</v>
+        <v>-0.093</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. IKPEZE</t>
+          <t>P. HARGUINDEY MANEIRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0012</v>
+        <v>-1.1669</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1157</v>
+        <v>-2.5617</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1146</v>
+        <v>1.3948</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4867</v>
+        <v>-1.6125</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0582</v>
+        <v>-1.4308</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5448</v>
+        <v>-0.1816</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1281</v>
+        <v>-1.19</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0492</v>
+        <v>-0.5187</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0789</v>
+        <v>-0.6713</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3585</v>
+        <v>-0.4224</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1074</v>
+        <v>-0.9121</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4659</v>
+        <v>0.4897</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.4107</v>
+        <v>0.2053</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.2321</v>
+        <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>2.2588</v>
       </c>
       <c r="S6" t="n">
-        <v>0.582</v>
+        <v>0.4804</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0118</v>
+        <v>0.6817</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5937</v>
+        <v>-0.2013</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.6591</v>
+        <v>-0.2402</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.6591</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. HARGUINDEY MANEIRO</t>
+          <t>A. IKPEZE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3793</v>
+        <v>-1.3429</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.4184</v>
+        <v>-1.2203</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0391</v>
+        <v>-0.1226</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6125</v>
+        <v>0.4867</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.4308</v>
+        <v>-0.0582</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1816</v>
+        <v>0.5448</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.19</v>
+        <v>0.1281</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.5187</v>
+        <v>0.0492</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6713</v>
+        <v>0.0789</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4224</v>
+        <v>0.3585</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9121</v>
+        <v>-0.1074</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4897</v>
+        <v>0.4659</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2053</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0534</v>
+        <v>-1.2321</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2588</v>
+        <v>0.8214</v>
       </c>
       <c r="S7" t="n">
-        <v>0.268</v>
+        <v>0.2402</v>
       </c>
       <c r="T7" t="n">
-        <v>0.825</v>
+        <v>-0.1164</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5570000000000001</v>
+        <v>0.3566</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2402</v>
+        <v>-1.6591</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2402</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5688</v>
+        <v>-1.4576</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.7465</v>
+        <v>-2.576</v>
       </c>
       <c r="F8" t="n">
-        <v>1.1777</v>
+        <v>1.1184</v>
       </c>
       <c r="G8" t="n">
         <v>-0.956</v>
@@ -1078,13 +1078,13 @@
         <v>0.616</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0235</v>
+        <v>-0.9124</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.527</v>
+        <v>-0.3565</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4966</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.721</v>
+        <v>-2.4023</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.7653</v>
+        <v>-2.5948</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0442</v>
+        <v>0.1925</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8869</v>
@@ -1156,13 +1156,13 @@
         <v>0.4107</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1914</v>
+        <v>-0.8727</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6587</v>
+        <v>-0.4882</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5327</v>
+        <v>-0.3845</v>
       </c>
       <c r="V9" t="n">
         <v>1.1786</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8536</v>
+        <v>-2.9105</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4896</v>
+        <v>-2.6058</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.364</v>
+        <v>-0.3047</v>
       </c>
       <c r="G10" t="n">
         <v>-0.646</v>
@@ -1234,13 +1234,13 @@
         <v>1.0267</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-0.6916</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0272</v>
+        <v>-0.1434</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6074000000000001</v>
+        <v>-0.5481</v>
       </c>
       <c r="V10" t="n">
         <v>0.4805</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. PRIOR RUIZ</t>
+          <t>A. HARO VAL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.7181</v>
+        <v>-3.1856</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1901</v>
+        <v>-3.6767</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.528</v>
+        <v>0.4911</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.2031</v>
+        <v>-2.9512</v>
       </c>
       <c r="H11" t="n">
-        <v>-3.2375</v>
+        <v>-1.5408</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.9656</v>
+        <v>-1.4104</v>
       </c>
       <c r="J11" t="n">
-        <v>-3.3884</v>
+        <v>-2.1656</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.3752</v>
+        <v>-0.126</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0131</v>
+        <v>-2.0396</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8148</v>
+        <v>-0.7856</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.8623</v>
+        <v>-1.4148</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0475</v>
+        <v>0.6291</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.2053</v>
+        <v>-0.616</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.0267</v>
+        <v>-2.2588</v>
       </c>
       <c r="R11" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1626</v>
+        <v>-0.0988</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0464</v>
+        <v>0.2672</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1163</v>
+        <v>-0.366</v>
       </c>
       <c r="V11" t="n">
-        <v>1.5277</v>
+        <v>0.4805</v>
       </c>
       <c r="W11" t="n">
-        <v>1.1786</v>
+        <v>0.4805</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. HARO VAL</t>
+          <t>A. PRIOR RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1476</v>
+        <v>-3.7956</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5794</v>
+        <v>-3.2675</v>
       </c>
       <c r="F12" t="n">
-        <v>0.4318</v>
+        <v>-0.528</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.9512</v>
+        <v>-5.2031</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.5408</v>
+        <v>-3.2375</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.4104</v>
+        <v>-1.9656</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.1656</v>
+        <v>-3.3884</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.126</v>
+        <v>-1.3752</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.0396</v>
+        <v>-2.0131</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7856</v>
+        <v>-1.8148</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4148</v>
+        <v>-1.8623</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6291</v>
+        <v>0.0475</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.616</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2588</v>
+        <v>-1.0267</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0608</v>
+        <v>0.0852</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6355</v>
+        <v>-0.0311</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4252</v>
+        <v>0.1163</v>
       </c>
       <c r="V12" t="n">
-        <v>0.4805</v>
+        <v>1.5277</v>
       </c>
       <c r="W12" t="n">
-        <v>0.4805</v>
+        <v>1.1786</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.197999999999999</v>
+        <v>-3.209900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.4993</v>
+        <v>-7.5112</v>
       </c>
       <c r="F13" t="n">
-        <v>4.3013</v>
+        <v>4.301500000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3146</v>
@@ -1450,13 +1450,13 @@
         <v>-2.9236</v>
       </c>
       <c r="M13" t="n">
-        <v>-5.0554</v>
+        <v>-5.055400000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>-9.136100000000001</v>
+        <v>-9.136099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>4.0805</v>
+        <v>4.080500000000001</v>
       </c>
       <c r="P13" t="n">
         <v>-1.0267</v>
@@ -1468,16 +1468,16 @@
         <v>14.3739</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9880000000000001</v>
+        <v>-9.999999999971143e-05</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5796000000000001</v>
+        <v>1.5677</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5676</v>
+        <v>-1.5677</v>
       </c>
       <c r="V13" t="n">
-        <v>0.1314000000000005</v>
+        <v>0.1314000000000004</v>
       </c>
       <c r="W13" t="n">
         <v>3.580900000000001</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>F. ADEBAYO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7205</v>
+        <v>3.5604</v>
       </c>
       <c r="E14" t="n">
-        <v>1.205</v>
+        <v>3.8211</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5154</v>
+        <v>-0.2607</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.0611</v>
+        <v>3.4116</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5089</v>
+        <v>2.8035</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.5522</v>
+        <v>0.6081</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1584</v>
+        <v>5.2126</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7373</v>
+        <v>4.6076</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.579</v>
+        <v>0.605</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.2194</v>
+        <v>-1.8011</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.2462</v>
+        <v>-1.8041</v>
       </c>
       <c r="O14" t="n">
-        <v>0.0268</v>
+        <v>0.003</v>
       </c>
       <c r="P14" t="n">
         <v>0.4107</v>
@@ -1546,28 +1546,28 @@
         <v>2.4641</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7733</v>
+        <v>1.2659</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2008</v>
+        <v>0.5305</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5726</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>2.5975</v>
+        <v>-1.5277</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8993</v>
+        <v>0.1314</v>
       </c>
       <c r="X14" t="n">
-        <v>0.6982</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>F. ADEBAYO</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.3565</v>
+        <v>2.9167</v>
       </c>
       <c r="E15" t="n">
-        <v>3.9257</v>
+        <v>0.3682</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5693</v>
+        <v>2.5485</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4116</v>
+        <v>-1.0611</v>
       </c>
       <c r="H15" t="n">
-        <v>2.8035</v>
+        <v>-0.5089</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6081</v>
+        <v>-0.5522</v>
       </c>
       <c r="J15" t="n">
-        <v>5.2126</v>
+        <v>0.1584</v>
       </c>
       <c r="K15" t="n">
-        <v>4.6076</v>
+        <v>0.7373</v>
       </c>
       <c r="L15" t="n">
-        <v>0.605</v>
+        <v>-0.579</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.8011</v>
+        <v>-1.2194</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8041</v>
+        <v>-1.2462</v>
       </c>
       <c r="O15" t="n">
-        <v>0.003</v>
+        <v>0.0268</v>
       </c>
       <c r="P15" t="n">
         <v>0.4107</v>
@@ -1624,22 +1624,22 @@
         <v>2.4641</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0619</v>
+        <v>0.9696</v>
       </c>
       <c r="T15" t="n">
-        <v>0.6351</v>
+        <v>0.3639</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4268</v>
+        <v>0.6056</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.5277</v>
+        <v>2.5975</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1314</v>
+        <v>1.8993</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.6591</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.2841</v>
+        <v>2.0348</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2412</v>
+        <v>-0.1772</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0429</v>
+        <v>2.2121</v>
       </c>
       <c r="G16" t="n">
         <v>1.2804</v>
@@ -1702,13 +1702,13 @@
         <v>1.4374</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5931</v>
+        <v>0.3438</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5461</v>
+        <v>0.1277</v>
       </c>
       <c r="U16" t="n">
-        <v>0.047</v>
+        <v>0.2161</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.2378</v>
+        <v>1.1785</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3744</v>
+        <v>-0.7927999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6123</v>
+        <v>1.9714</v>
       </c>
       <c r="G17" t="n">
         <v>1.8624</v>
@@ -1780,13 +1780,13 @@
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2317</v>
+        <v>0.1724</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6778</v>
+        <v>0.2594</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4461</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2402</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3819</v>
+        <v>1.1298</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.6513</v>
+        <v>-0.2329</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0332</v>
+        <v>1.3627</v>
       </c>
       <c r="G18" t="n">
         <v>0.5643</v>
@@ -1858,13 +1858,13 @@
         <v>1.8481</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.435</v>
+        <v>0.3129</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3643</v>
+        <v>0.0541</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0707</v>
+        <v>0.2588</v>
       </c>
       <c r="V18" t="n">
         <v>0.4579</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1941</v>
+        <v>0.1906</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3705</v>
+        <v>-0.4751</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5646</v>
+        <v>0.6657</v>
       </c>
       <c r="G19" t="n">
         <v>0.6622</v>
@@ -1936,13 +1936,13 @@
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1295</v>
+        <v>0.1259</v>
       </c>
       <c r="T19" t="n">
-        <v>0.244</v>
+        <v>0.1394</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1145</v>
+        <v>-0.0134</v>
       </c>
       <c r="V19" t="n">
         <v>-1.4189</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2166</v>
+        <v>-0.09810000000000001</v>
       </c>
       <c r="E20" t="n">
         <v>-0.212</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0046</v>
+        <v>0.114</v>
       </c>
       <c r="G20" t="n">
         <v>-0.164</v>
@@ -2014,13 +2014,13 @@
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.258</v>
+        <v>-0.1395</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3294</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0713</v>
+        <v>0.1899</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.5059</v>
+        <v>-1.2019</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.6628</v>
+        <v>-2.0352</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1568</v>
+        <v>0.8333</v>
       </c>
       <c r="G21" t="n">
         <v>0.5765</v>
@@ -2092,13 +2092,13 @@
         <v>2.2588</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2343</v>
+        <v>0.0697</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.0583</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5484</v>
+        <v>0.1281</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2544</v>
+        <v>-2.7236</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.4023</v>
+        <v>-4.5655</v>
       </c>
       <c r="F22" t="n">
-        <v>1.148</v>
+        <v>1.8419</v>
       </c>
       <c r="G22" t="n">
         <v>-4.8177</v>
@@ -2170,13 +2170,13 @@
         <v>2.4641</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8741</v>
+        <v>0.6567</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3566</v>
+        <v>0.4802</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5175</v>
+        <v>0.1765</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>4.198</v>
+        <v>6.987200000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.301400000000001</v>
+        <v>-4.3014</v>
       </c>
       <c r="F23" t="n">
-        <v>8.4993</v>
+        <v>11.2889</v>
       </c>
       <c r="G23" t="n">
         <v>2.3146</v>
@@ -2248,13 +2248,13 @@
         <v>15.4007</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9881000000000001</v>
+        <v>3.7774</v>
       </c>
       <c r="T23" t="n">
         <v>1.5675</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5794999999999999</v>
+        <v>2.21</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1314</v>
